--- a/output/Tables/Sensitivity analyses/HIA_DRF_sensitivity_1000replicate.xlsx
+++ b/output/Tables/Sensitivity analyses/HIA_DRF_sensitivity_1000replicate.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>19270.672</v>
+        <v>19503.78</v>
       </c>
       <c r="C2">
-        <v>18310.25</v>
+        <v>18537.518</v>
       </c>
       <c r="D2">
-        <v>20241.895</v>
+        <v>20468.299</v>
       </c>
       <c r="E2">
-        <v>202863.996</v>
+        <v>204035.47</v>
       </c>
       <c r="F2">
-        <v>196543.072</v>
+        <v>197654.153</v>
       </c>
       <c r="G2">
-        <v>209209.694</v>
+        <v>210461.723</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>2564.839</v>
+        <v>2566.432</v>
       </c>
       <c r="C3">
-        <v>2381.799</v>
+        <v>2382.995</v>
       </c>
       <c r="D3">
-        <v>2756.768</v>
+        <v>2757.906</v>
       </c>
       <c r="E3">
-        <v>4318.133</v>
+        <v>2005.253</v>
       </c>
       <c r="F3">
-        <v>3970.713</v>
+        <v>1860.475</v>
       </c>
       <c r="G3">
-        <v>4686.567</v>
+        <v>2159.205</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>2137.236</v>
+        <v>2149.405</v>
       </c>
       <c r="C4">
-        <v>2033.675</v>
+        <v>2045.71</v>
       </c>
       <c r="D4">
-        <v>2243.339</v>
+        <v>2257.345</v>
       </c>
       <c r="E4">
-        <v>2635.507000000001</v>
+        <v>1216.502</v>
       </c>
       <c r="F4">
-        <v>2524.905</v>
+        <v>1160.821</v>
       </c>
       <c r="G4">
-        <v>2750.237</v>
+        <v>1274.188</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>41047.704</v>
+        <v>41244.65100000001</v>
       </c>
       <c r="C5">
-        <v>39443.488</v>
+        <v>39662.47199999999</v>
       </c>
       <c r="D5">
-        <v>42659.98</v>
+        <v>42834.671</v>
       </c>
       <c r="E5">
-        <v>36619.72099999999</v>
+        <v>56446.80900000001</v>
       </c>
       <c r="F5">
-        <v>35349.97199999999</v>
+        <v>54481.049</v>
       </c>
       <c r="G5">
-        <v>37897.425</v>
+        <v>58423.515</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>13374.952</v>
+        <v>13479.604</v>
       </c>
       <c r="C6">
-        <v>12986.887</v>
+        <v>13085.563</v>
       </c>
       <c r="D6">
-        <v>13764.627</v>
+        <v>13878.939</v>
       </c>
       <c r="E6">
-        <v>26079.172</v>
+        <v>24571.188</v>
       </c>
       <c r="F6">
-        <v>25300.53999999999</v>
+        <v>23784.819</v>
       </c>
       <c r="G6">
-        <v>26868.49799999999</v>
+        <v>25367.948</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>6948.093999999999</v>
+        <v>7023.279</v>
       </c>
       <c r="C7">
-        <v>6541.084999999999</v>
+        <v>6621.550999999998</v>
       </c>
       <c r="D7">
-        <v>7361.279</v>
+        <v>7432.885</v>
       </c>
       <c r="E7">
-        <v>11721.661</v>
+        <v>8004.993</v>
       </c>
       <c r="F7">
-        <v>11178.246</v>
+        <v>7537.941000000001</v>
       </c>
       <c r="G7">
-        <v>12280.096</v>
+        <v>8483.770999999999</v>
       </c>
     </row>
     <row r="8">
@@ -548,47 +548,47 @@
         </is>
       </c>
       <c r="B8">
-        <v>224418.856</v>
+        <v>225745.638</v>
       </c>
       <c r="C8">
-        <v>218479.514</v>
+        <v>219734.5420000001</v>
       </c>
       <c r="D8">
-        <v>230356.4469999999</v>
+        <v>231730.379</v>
       </c>
       <c r="E8">
-        <v>72400.62299999999</v>
+        <v>84553.87100000001</v>
       </c>
       <c r="F8">
-        <v>69674.46400000001</v>
+        <v>81461.851</v>
       </c>
       <c r="G8">
-        <v>75196.823</v>
+        <v>87694.54599999997</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>Chronic diseases</t>
         </is>
       </c>
       <c r="B9">
-        <v>290491.681</v>
+        <v>292209.009</v>
       </c>
       <c r="C9">
-        <v>281866.448</v>
+        <v>283532.833</v>
       </c>
       <c r="D9">
-        <v>299142.4399999999</v>
+        <v>300892.1249999999</v>
       </c>
       <c r="E9">
-        <v>153774.817</v>
+        <v>176798.616</v>
       </c>
       <c r="F9">
-        <v>147998.84</v>
+        <v>170286.956</v>
       </c>
       <c r="G9">
-        <v>159679.646</v>
+        <v>183403.173</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>309762.353</v>
+        <v>311712.789</v>
       </c>
       <c r="C10">
-        <v>300176.698</v>
+        <v>302070.351</v>
       </c>
       <c r="D10">
-        <v>319384.3349999999</v>
+        <v>321360.4239999999</v>
       </c>
       <c r="E10">
-        <v>356638.813</v>
+        <v>380834.086</v>
       </c>
       <c r="F10">
-        <v>344541.9119999999</v>
+        <v>367941.1089999999</v>
       </c>
       <c r="G10">
-        <v>368889.34</v>
+        <v>393864.896</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Sensitivity analyses/HIA_DRF_sensitivity_1000replicate.xlsx
+++ b/output/Tables/Sensitivity analyses/HIA_DRF_sensitivity_1000replicate.xlsx
@@ -1,21 +1,80 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Sensitivity analyses/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{666FF137-A0DA-3E40-B874-CD3C0E98BD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>bc</t>
+  </si>
+  <si>
+    <t>cc</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>Chronic diseases</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +122,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +174,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +208,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +243,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,52 +419,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
       </c>
       <c r="B2">
         <v>19503.78</v>
@@ -404,101 +463,93 @@
         <v>18537.518</v>
       </c>
       <c r="D2">
-        <v>20468.299</v>
+        <v>20468.298999999999</v>
       </c>
       <c r="E2">
         <v>204035.47</v>
       </c>
       <c r="F2">
-        <v>197654.153</v>
+        <v>197654.15299999999</v>
       </c>
       <c r="G2">
         <v>210461.723</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>2566.432</v>
+        <v>2566.4319999999998</v>
       </c>
       <c r="C3">
-        <v>2382.995</v>
+        <v>2382.9949999999999</v>
       </c>
       <c r="D3">
-        <v>2757.906</v>
+        <v>2757.9059999999999</v>
       </c>
       <c r="E3">
-        <v>2005.253</v>
+        <v>2005.2529999999999</v>
       </c>
       <c r="F3">
-        <v>1860.475</v>
+        <v>1860.4749999999999</v>
       </c>
       <c r="G3">
-        <v>2159.205</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
+        <v>2159.2049999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>2149.405</v>
+        <v>2149.4050000000002</v>
       </c>
       <c r="C4">
         <v>2045.71</v>
       </c>
       <c r="D4">
-        <v>2257.345</v>
+        <v>2257.3449999999998</v>
       </c>
       <c r="E4">
         <v>1216.502</v>
       </c>
       <c r="F4">
-        <v>1160.821</v>
+        <v>1160.8209999999999</v>
       </c>
       <c r="G4">
-        <v>1274.188</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+        <v>1274.1880000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>41244.65100000001</v>
+        <v>41244.651000000013</v>
       </c>
       <c r="C5">
-        <v>39662.47199999999</v>
+        <v>39662.471999999987</v>
       </c>
       <c r="D5">
-        <v>42834.671</v>
+        <v>42834.671000000002</v>
       </c>
       <c r="E5">
-        <v>56446.80900000001</v>
+        <v>56446.809000000008</v>
       </c>
       <c r="F5">
-        <v>54481.049</v>
+        <v>54481.048999999999</v>
       </c>
       <c r="G5">
-        <v>58423.515</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+        <v>58423.514999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>11</v>
       </c>
       <c r="B6">
-        <v>13479.604</v>
+        <v>13479.603999999999</v>
       </c>
       <c r="C6">
         <v>13085.563</v>
@@ -507,7 +558,7 @@
         <v>13878.939</v>
       </c>
       <c r="E6">
-        <v>24571.188</v>
+        <v>24571.187999999998</v>
       </c>
       <c r="F6">
         <v>23784.819</v>
@@ -516,104 +567,96 @@
         <v>25367.948</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>12</v>
       </c>
       <c r="B7">
-        <v>7023.279</v>
+        <v>7023.2790000000005</v>
       </c>
       <c r="C7">
-        <v>6621.550999999998</v>
+        <v>6621.5509999999977</v>
       </c>
       <c r="D7">
-        <v>7432.885</v>
+        <v>7432.8850000000002</v>
       </c>
       <c r="E7">
-        <v>8004.993</v>
+        <v>8004.9930000000004</v>
       </c>
       <c r="F7">
-        <v>7537.941000000001</v>
+        <v>7537.9410000000007</v>
       </c>
       <c r="G7">
-        <v>8483.770999999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
+        <v>8483.7709999999988</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>13</v>
       </c>
       <c r="B8">
-        <v>225745.638</v>
+        <v>225745.63800000001</v>
       </c>
       <c r="C8">
         <v>219734.5420000001</v>
       </c>
       <c r="D8">
-        <v>231730.379</v>
+        <v>231730.37899999999</v>
       </c>
       <c r="E8">
-        <v>84553.87100000001</v>
+        <v>84553.871000000014</v>
       </c>
       <c r="F8">
-        <v>81461.851</v>
+        <v>81461.850999999995</v>
       </c>
       <c r="G8">
-        <v>87694.54599999997</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Chronic diseases</t>
-        </is>
+        <v>87694.545999999973</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>14</v>
       </c>
       <c r="B9">
-        <v>292209.009</v>
+        <v>292209.00900000002</v>
       </c>
       <c r="C9">
-        <v>283532.833</v>
+        <v>283532.83299999998</v>
       </c>
       <c r="D9">
-        <v>300892.1249999999</v>
+        <v>300892.12499999988</v>
       </c>
       <c r="E9">
-        <v>176798.616</v>
+        <v>176798.61600000001</v>
       </c>
       <c r="F9">
-        <v>170286.956</v>
+        <v>170286.95600000001</v>
       </c>
       <c r="G9">
-        <v>183403.173</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>183403.17300000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>15</v>
       </c>
       <c r="B10">
-        <v>311712.789</v>
+        <v>311712.78899999999</v>
       </c>
       <c r="C10">
-        <v>302070.351</v>
+        <v>302070.35100000002</v>
       </c>
       <c r="D10">
-        <v>321360.4239999999</v>
+        <v>321360.42399999988</v>
       </c>
       <c r="E10">
-        <v>380834.086</v>
+        <v>380834.08600000001</v>
       </c>
       <c r="F10">
-        <v>367941.1089999999</v>
+        <v>367941.10899999988</v>
       </c>
       <c r="G10">
-        <v>393864.896</v>
+        <v>393864.89600000001</v>
       </c>
     </row>
   </sheetData>
